--- a/public/upload/export_excel/รายงานจองรายเดือน08-2025.xlsx
+++ b/public/upload/export_excel/รายงานจองรายเดือน08-2025.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
   <si>
     <t>ห้อง</t>
   </si>
@@ -96,6 +96,60 @@
   </si>
   <si>
     <t>RE202508000016</t>
+  </si>
+  <si>
+    <t>A107</t>
+  </si>
+  <si>
+    <t>RE202508000022</t>
+  </si>
+  <si>
+    <t>A201</t>
+  </si>
+  <si>
+    <t>อุไร กฤษณะ</t>
+  </si>
+  <si>
+    <t>RE202508000023</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>A202</t>
+  </si>
+  <si>
+    <t>RE202508000024</t>
+  </si>
+  <si>
+    <t>A203</t>
+  </si>
+  <si>
+    <t>RE202508000025</t>
+  </si>
+  <si>
+    <t>A204</t>
+  </si>
+  <si>
+    <t>RE202508000026</t>
+  </si>
+  <si>
+    <t>A205</t>
+  </si>
+  <si>
+    <t>ทิพย์วรรณ ธีรพล</t>
+  </si>
+  <si>
+    <t>RE202508000034</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>A206</t>
+  </si>
+  <si>
+    <t>RE202508000035</t>
   </si>
 </sst>
 </file>
@@ -438,7 +492,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -652,6 +706,216 @@
         <v>1000.0</v>
       </c>
       <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1000.0</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>320.0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>320.0</v>
+      </c>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1">
+        <v>320.0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>320.0</v>
+      </c>
+      <c r="J14" s="1"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
